--- a/outputs/gr_SSP2_gdppc_baseyear.xlsx
+++ b/outputs/gr_SSP2_gdppc_baseyear.xlsx
@@ -1,171 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>2030</t>
-  </si>
-  <si>
-    <t>2035</t>
-  </si>
-  <si>
-    <t>2040</t>
-  </si>
-  <si>
-    <t>2045</t>
-  </si>
-  <si>
-    <t>2050</t>
-  </si>
-  <si>
-    <t>2060</t>
-  </si>
-  <si>
-    <t>2070</t>
-  </si>
-  <si>
-    <t>2080</t>
-  </si>
-  <si>
-    <t>2090</t>
-  </si>
-  <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>OMNIA</t>
-  </si>
-  <si>
-    <t>AFE</t>
-  </si>
-  <si>
-    <t>AFN</t>
-  </si>
-  <si>
-    <t>AFW</t>
-  </si>
-  <si>
-    <t>AFZ</t>
-  </si>
-  <si>
-    <t>ANZ</t>
-  </si>
-  <si>
-    <t>ASC</t>
-  </si>
-  <si>
-    <t>ASE</t>
-  </si>
-  <si>
-    <t>ASO</t>
-  </si>
-  <si>
-    <t>BRA</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>CHL</t>
-  </si>
-  <si>
-    <t>CHN</t>
-  </si>
-  <si>
-    <t>ENE</t>
-  </si>
-  <si>
-    <t>ENW</t>
-  </si>
-  <si>
-    <t>EUE</t>
-  </si>
-  <si>
-    <t>EUM</t>
-  </si>
-  <si>
-    <t>EUW</t>
-  </si>
-  <si>
-    <t>IDN</t>
-  </si>
-  <si>
-    <t>IND</t>
-  </si>
-  <si>
-    <t>JPN</t>
-  </si>
-  <si>
-    <t>LAM</t>
-  </si>
-  <si>
-    <t>MDA</t>
-  </si>
-  <si>
-    <t>MEA</t>
-  </si>
-  <si>
-    <t>MEX</t>
-  </si>
-  <si>
-    <t>NIG</t>
-  </si>
-  <si>
-    <t>RUS</t>
-  </si>
-  <si>
-    <t>SKT</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -180,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -496,1287 +420,1375 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>OMNIA</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2060</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>AFE</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
         <v>1.01898378089872</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>1.056054167143628</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>1.274828743862274</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1.524303785668471</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>1.801005203233857</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>2.126613940822494</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>2.512118134989028</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>3.518456549569003</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>4.926525205741543</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>6.816645367263123</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>9.250856253410587</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>12.32123283783019</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>AFN</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
         <v>1.050720573508157</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>1.092318843156508</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>1.256888594811049</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>1.482676637948949</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>1.744753711805719</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>2.048655954313024</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>2.403089569541938</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>3.295671969472858</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>4.416252655174958</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>5.703858486007075</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>7.168272090566834</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>8.864939586840663</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>AFW</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
         <v>1.029685181020873</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>1.074125658760796</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>1.201335606893897</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>1.410050473626429</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>1.648742633434483</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>1.931064435303152</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>2.26785154106023</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>3.151819401789651</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>4.380517039473537</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>6.023178401589689</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>8.172353517644376</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>10.95473234205594</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>AFZ</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.9515920409597837</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>0.9539717440278082</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>0.9851170714211314</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>1.081234243235392</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>1.21035962546449</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>1.372382903728791</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>1.567221747956423</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>2.068107985697981</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>2.739965149932412</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>3.611240201617432</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>4.725236768226054</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>6.103799933279284</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ANZ</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
         <v>1.050321068534034</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>1.067155982520192</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>1.155383574724332</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>1.264309468020607</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>1.378031609987429</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>1.497391238504088</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>1.615854579326033</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>1.855949259075641</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>2.112409760710338</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>2.365625516499755</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>2.616886028293902</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>2.86626883146891</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
         <v>1.081620026020254</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>1.152980872103788</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>1.319616848853089</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>1.498929973276417</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>1.666711508216061</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>1.823172280400531</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>1.982220511354684</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>2.372000335989781</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>2.881887499763495</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>3.471269194172891</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>4.169640831253668</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>4.999872917109442</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ASE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
         <v>1.011424463239229</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>1.065969180098096</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>1.214130950401203</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>1.38153791808556</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>1.539894724102063</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>1.698835314740028</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>1.865753393020239</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>2.247476851915022</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>2.716621096656002</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>3.257478779669349</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>3.880358246581919</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>4.60921372416332</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ASO</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
         <v>1.086351285236646</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>1.128248687555438</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>1.367142747668723</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>1.65782767465239</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>1.976300352172278</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>2.338858954423345</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>2.751565528102297</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>3.758204221577456</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>5.063190630219434</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>6.674794889563008</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>8.563888280168868</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>10.75116141108866</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
         <v>1.050948335355084</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>1.096127453574457</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>1.200303650952647</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>1.344502085825916</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>1.542961408956519</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>1.793582739518806</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>2.092203985720631</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>2.819147616674328</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>3.715095949181574</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>4.764965869866701</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>5.951603335978745</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>7.265146836126118</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.024193175124771</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>1.052672512700662</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>1.130010205673204</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>1.232669873869597</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>1.347202047208965</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>1.465222015318707</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>1.578943756758346</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>1.806810879730402</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>2.040772416545078</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>2.266087494769031</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>2.489115582530612</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>2.713278760591369</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
         <v>1.041119018394158</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>1.084402534198039</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>1.185995447079533</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>1.293080201398949</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>1.421726036818975</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>1.571120627739163</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>1.736116741773479</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>2.098982513725193</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>2.528574473857912</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>2.999833449294008</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>3.479807253202246</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>3.943933731970498</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
         <v>1.188849485651642</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>1.300657362259864</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>1.560183790314517</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>1.818689557220444</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>2.043456303555429</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>2.278978691226533</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>2.529124619376537</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>3.080017163995635</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>3.7035875227142</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>4.293039839244662</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>4.893861985627921</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>5.502245122520814</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ENE</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
         <v>0.9667805345525663</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>1.080537865283217</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>1.288477908150015</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>1.513721649820026</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>1.746276734357113</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>1.983811331264065</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>2.230252412425263</v>
       </c>
-      <c r="J14">
+      <c r="J14" t="n">
         <v>2.782207383115895</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="n">
         <v>3.421286369250823</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>4.108882632136494</v>
       </c>
-      <c r="M14">
+      <c r="M14" t="n">
         <v>4.866769639693755</v>
       </c>
-      <c r="N14">
+      <c r="N14" t="n">
         <v>5.731546408541748</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ENW</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
         <v>1.019069532651414</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>1.039915889141704</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>1.103382054993212</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>1.182417645736909</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>1.271268676912421</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="n">
         <v>1.36732338316507</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="n">
         <v>1.465045025215099</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="n">
         <v>1.678857073335572</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>1.908390601935732</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>2.11932577903973</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="n">
         <v>2.318894183037263</v>
       </c>
-      <c r="N15">
+      <c r="N15" t="n">
         <v>2.503881907200472</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EUE</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
         <v>1.086801876396176</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>1.147140742812218</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>1.352260463854438</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>1.526479522675315</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>1.682342714006781</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="n">
         <v>1.811957850504736</v>
       </c>
-      <c r="I16">
+      <c r="I16" t="n">
         <v>1.928078875749326</v>
       </c>
-      <c r="J16">
+      <c r="J16" t="n">
         <v>2.152955546072053</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="n">
         <v>2.386976501023012</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>2.600890606315038</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="n">
         <v>2.793120360433012</v>
       </c>
-      <c r="N16">
+      <c r="N16" t="n">
         <v>2.980769083442888</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>EUM</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
         <v>1.036788510856648</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>1.066489103121874</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>1.137539817339289</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>1.220186741188707</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>1.30632156999461</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="n">
         <v>1.394052244205846</v>
       </c>
-      <c r="I17">
+      <c r="I17" t="n">
         <v>1.482683436495938</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="n">
         <v>1.676555348971557</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>1.877598773626499</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>2.057848857095203</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="n">
         <v>2.226860871062114</v>
       </c>
-      <c r="N17">
+      <c r="N17" t="n">
         <v>2.394536564043595</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EUW</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
         <v>1.030127824242033</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>1.041730145384134</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>1.113685859342206</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>1.186540949712453</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>1.264264004398732</v>
       </c>
-      <c r="H18">
+      <c r="H18" t="n">
         <v>1.344991777947544</v>
       </c>
-      <c r="I18">
+      <c r="I18" t="n">
         <v>1.424433530765404</v>
       </c>
-      <c r="J18">
+      <c r="J18" t="n">
         <v>1.583008637342405</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="n">
         <v>1.74316643287064</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>1.888242141976134</v>
       </c>
-      <c r="M18">
+      <c r="M18" t="n">
         <v>2.018401966351732</v>
       </c>
-      <c r="N18">
+      <c r="N18" t="n">
         <v>2.132665132256121</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>IDN</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
         <v>1.088425449538143</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>1.188404597965649</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>1.477066841054633</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>1.77235273512147</v>
       </c>
-      <c r="G19">
+      <c r="G19" t="n">
         <v>2.064756971432042</v>
       </c>
-      <c r="H19">
+      <c r="H19" t="n">
         <v>2.354242198308298</v>
       </c>
-      <c r="I19">
+      <c r="I19" t="n">
         <v>2.642596059161859</v>
       </c>
-      <c r="J19">
+      <c r="J19" t="n">
         <v>3.256225378251107</v>
       </c>
-      <c r="K19">
+      <c r="K19" t="n">
         <v>3.915535440952099</v>
       </c>
-      <c r="L19">
+      <c r="L19" t="n">
         <v>4.600332634207909</v>
       </c>
-      <c r="M19">
+      <c r="M19" t="n">
         <v>5.317090037062797</v>
       </c>
-      <c r="N19">
+      <c r="N19" t="n">
         <v>6.073407030566458</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
         <v>1.155794605751773</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>1.296852845471437</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>1.688788386417165</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>2.066169445963446</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>2.471750342955668</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="n">
         <v>2.913890948539442</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>3.400977753516158</v>
       </c>
-      <c r="J20">
+      <c r="J20" t="n">
         <v>4.524487015011404</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="n">
         <v>5.833883555352072</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>7.289052593213946</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="n">
         <v>8.83795585211967</v>
       </c>
-      <c r="N20">
+      <c r="N20" t="n">
         <v>10.46831813380034</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
         <v>1.030665321612009</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>1.055607848591225</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>1.119194167898424</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>1.200126551403795</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>1.279471592928506</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="n">
         <v>1.36525007824586</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>1.457706003933886</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="n">
         <v>1.645106564980277</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="n">
         <v>1.840366862866323</v>
       </c>
-      <c r="L21">
+      <c r="L21" t="n">
         <v>2.040607519720751</v>
       </c>
-      <c r="M21">
+      <c r="M21" t="n">
         <v>2.238150336718367</v>
       </c>
-      <c r="N21">
+      <c r="N21" t="n">
         <v>2.42821019951719</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
         <v>1.04192040880012</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>1.078553625204291</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>1.256223236724994</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>1.457910204443165</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>1.677444609070642</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="n">
         <v>1.902933799607442</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>2.128084103592254</v>
       </c>
-      <c r="J22">
+      <c r="J22" t="n">
         <v>2.626399085932072</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="n">
         <v>3.242578750021501</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>3.966746679341759</v>
       </c>
-      <c r="M22">
+      <c r="M22" t="n">
         <v>4.791937067334739</v>
       </c>
-      <c r="N22">
+      <c r="N22" t="n">
         <v>5.726496330882443</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>MDA</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
         <v>1.182273724115081</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>1.222360336427428</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>1.393484968202815</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>1.5756879630356</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>1.742865776988031</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="n">
         <v>1.90424570615915</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>2.061566903137951</v>
       </c>
-      <c r="J23">
+      <c r="J23" t="n">
         <v>2.388571187887384</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="n">
         <v>2.706179895904016</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>2.994650417457832</v>
       </c>
-      <c r="M23">
+      <c r="M23" t="n">
         <v>3.282622791282655</v>
       </c>
-      <c r="N23">
+      <c r="N23" t="n">
         <v>3.588512966447579</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>MEA</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
         <v>1.021189833754579</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>1.053078587389239</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>1.167384273222261</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>1.28204411093976</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>1.394913991075881</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="n">
         <v>1.501088590417338</v>
       </c>
-      <c r="I24">
+      <c r="I24" t="n">
         <v>1.604508690764668</v>
       </c>
-      <c r="J24">
+      <c r="J24" t="n">
         <v>1.831132326470528</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="n">
         <v>2.102190350003919</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>2.396838316696814</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="n">
         <v>2.72003081390275</v>
       </c>
-      <c r="N24">
+      <c r="N24" t="n">
         <v>3.088449989945663</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
         <v>1.00588703275171</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>1.019020858421264</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>1.093274289580122</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>1.210392219222166</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>1.343637837093965</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="n">
         <v>1.494873426237881</v>
       </c>
-      <c r="I25">
+      <c r="I25" t="n">
         <v>1.662146523231085</v>
       </c>
-      <c r="J25">
+      <c r="J25" t="n">
         <v>2.026398514423574</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="n">
         <v>2.420019506589242</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>2.828066808049408</v>
       </c>
-      <c r="M25">
+      <c r="M25" t="n">
         <v>3.225137873366788</v>
       </c>
-      <c r="N25">
+      <c r="N25" t="n">
         <v>3.594420372469572</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>NIG</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
         <v>0.980710294513193</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>0.9941357427805882</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>1.037237261892411</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>1.174562893422602</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>1.323801585593488</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="n">
         <v>1.496178320865005</v>
       </c>
-      <c r="I26">
+      <c r="I26" t="n">
         <v>1.701437757863302</v>
       </c>
-      <c r="J26">
+      <c r="J26" t="n">
         <v>2.245902601090354</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="n">
         <v>2.99271095561915</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>3.959093093386854</v>
       </c>
-      <c r="M26">
+      <c r="M26" t="n">
         <v>5.200076315792261</v>
       </c>
-      <c r="N26">
+      <c r="N26" t="n">
         <v>6.793757688204608</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
         <v>1.054479568998508</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>1.107833672143819</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>1.194602187054616</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>1.327650306464222</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>1.463744581765388</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="n">
         <v>1.598340506879954</v>
       </c>
-      <c r="I27">
+      <c r="I27" t="n">
         <v>1.7318417410761</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="n">
         <v>2.058781650924607</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>2.461423268353208</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>2.898659302522185</v>
       </c>
-      <c r="M27">
+      <c r="M27" t="n">
         <v>3.390071850986528</v>
       </c>
-      <c r="N27">
+      <c r="N27" t="n">
         <v>3.965805531332063</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
         <v>1.106910291317773</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>1.171069695493081</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>1.320350608901853</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>1.429574576379877</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>1.507324077242014</v>
       </c>
-      <c r="H28">
+      <c r="H28" t="n">
         <v>1.568419280358553</v>
       </c>
-      <c r="I28">
+      <c r="I28" t="n">
         <v>1.618312581017223</v>
       </c>
-      <c r="J28">
+      <c r="J28" t="n">
         <v>1.717501582049469</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>1.822681070924138</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>1.913842509531172</v>
       </c>
-      <c r="M28">
+      <c r="M28" t="n">
         <v>1.991401776972624</v>
       </c>
-      <c r="N28">
+      <c r="N28" t="n">
         <v>2.065887707130442</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
         <v>1.073863175959788</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>1.119478998824473</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>1.20997452426939</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>1.278625814577139</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>1.340460928132614</v>
       </c>
-      <c r="H29">
+      <c r="H29" t="n">
         <v>1.399806672670358</v>
       </c>
-      <c r="I29">
+      <c r="I29" t="n">
         <v>1.457874090745376</v>
       </c>
-      <c r="J29">
+      <c r="J29" t="n">
         <v>1.581433313533562</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="n">
         <v>1.707485028829676</v>
       </c>
-      <c r="L29">
+      <c r="L29" t="n">
         <v>1.832662434856018</v>
       </c>
-      <c r="M29">
+      <c r="M29" t="n">
         <v>1.970228599784897</v>
       </c>
-      <c r="N29">
+      <c r="N29" t="n">
         <v>2.118428706286187</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/gr_SSP2_gdppc_baseyear.xlsx
+++ b/outputs/gr_SSP2_gdppc_baseyear.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,79 +417,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>OMNIA</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>2035</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2040</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>2045</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>2050</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>2060</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2070</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>2080</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>2090</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>2100</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>AFE</t>
         </is>
@@ -547,7 +535,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>AFN</t>
         </is>
@@ -593,7 +581,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>AFW</t>
         </is>
@@ -639,7 +627,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>AFZ</t>
         </is>
@@ -685,7 +673,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>ANZ</t>
         </is>
@@ -731,7 +719,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>ASC</t>
         </is>
@@ -777,7 +765,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>ASE</t>
         </is>
@@ -823,7 +811,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>ASO</t>
         </is>
@@ -869,7 +857,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>BRA</t>
         </is>
@@ -915,7 +903,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
@@ -961,7 +949,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>CHL</t>
         </is>
@@ -1007,7 +995,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>CHN</t>
         </is>
@@ -1053,7 +1041,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>ENE</t>
         </is>
@@ -1099,7 +1087,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ENW</t>
         </is>
@@ -1145,7 +1133,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>EUE</t>
         </is>
@@ -1191,7 +1179,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>EUM</t>
         </is>
@@ -1237,7 +1225,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>EUW</t>
         </is>
@@ -1283,7 +1271,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>IDN</t>
         </is>
@@ -1329,7 +1317,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>IND</t>
         </is>
@@ -1375,7 +1363,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>JPN</t>
         </is>
@@ -1421,7 +1409,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>LAM</t>
         </is>
@@ -1467,7 +1455,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>MDA</t>
         </is>
@@ -1513,7 +1501,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>MEA</t>
         </is>
@@ -1559,7 +1547,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>MEX</t>
         </is>
@@ -1605,7 +1593,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>NIG</t>
         </is>
@@ -1651,7 +1639,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>RUS</t>
         </is>
@@ -1697,7 +1685,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>SKT</t>
         </is>
@@ -1743,7 +1731,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
